--- a/cmnrag-website/paiban-data/采访中心综合表格_2026值班.xlsx
+++ b/cmnrag-website/paiban-data/采访中心综合表格_2026值班.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD1B1B4-FCD1-4750-A28F-1734C06C390C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C387F30-9DA7-4CB6-B121-987D2DB92DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="58">
   <si>
     <t>值班日期</t>
   </si>
@@ -111,21 +111,12 @@
     <t>周刊</t>
   </si>
   <si>
-    <t>郭笑羽,王畅</t>
-  </si>
-  <si>
     <t>2.8 以后黄彬休假</t>
   </si>
   <si>
     <t>2.7-2.10  王亮 休假</t>
   </si>
   <si>
-    <t>吴彤,史光浩</t>
-  </si>
-  <si>
-    <t>做节后见报第一期（2.24见报）</t>
-  </si>
-  <si>
     <t>情人节上班</t>
   </si>
   <si>
@@ -187,6 +178,22 @@
   </si>
   <si>
     <t>文科,郭笑羽</t>
+  </si>
+  <si>
+    <t>郭笑羽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>二班合作：王畅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>二班合作：史光浩；做节后见报第一期（2.24见报）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴彤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1192,7 +1199,10 @@
         <v>12</v>
       </c>
       <c r="D56" t="s">
-        <v>31</v>
+        <v>54</v>
+      </c>
+      <c r="E56" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="25.5" customHeight="1">
@@ -1219,7 +1229,7 @@
         <v>46061</v>
       </c>
       <c r="E59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="25.5" customHeight="1">
@@ -1236,7 +1246,7 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="25.5" customHeight="1">
@@ -1292,10 +1302,10 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E64" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="25.5" customHeight="1">
@@ -1303,7 +1313,7 @@
         <v>46067</v>
       </c>
       <c r="E65" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="25.5" customHeight="1">
@@ -1311,7 +1321,7 @@
         <v>46068</v>
       </c>
       <c r="E66" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="25.5" customHeight="1">
@@ -1322,7 +1332,7 @@
         <v>5</v>
       </c>
       <c r="E67" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="25.5" customHeight="1">
@@ -1333,7 +1343,7 @@
         <v>8</v>
       </c>
       <c r="E68" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="25.5" customHeight="1">
@@ -1344,7 +1354,7 @@
         <v>11</v>
       </c>
       <c r="E69" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="25.5" customHeight="1">
@@ -1355,7 +1365,7 @@
         <v>14</v>
       </c>
       <c r="E70" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="25.5" customHeight="1">
@@ -1366,7 +1376,7 @@
         <v>17</v>
       </c>
       <c r="E71" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="25.5" customHeight="1">
@@ -1374,7 +1384,7 @@
         <v>46074</v>
       </c>
       <c r="E72" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="25.5" customHeight="1">
@@ -1382,7 +1392,7 @@
         <v>46075</v>
       </c>
       <c r="E73" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="25.5" customHeight="1">
@@ -1393,7 +1403,7 @@
         <v>5</v>
       </c>
       <c r="E74" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="25.5" customHeight="1">
@@ -1452,7 +1462,7 @@
         <v>18</v>
       </c>
       <c r="E78" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="25.5" customHeight="1">
@@ -1460,7 +1470,7 @@
         <v>46081</v>
       </c>
       <c r="E79" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="25.5" customHeight="1">
@@ -1476,7 +1486,7 @@
         <v>5</v>
       </c>
       <c r="C81" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D81" t="s">
         <v>15</v>
@@ -1490,7 +1500,7 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -1570,7 +1580,7 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -1587,7 +1597,7 @@
         <v>19</v>
       </c>
       <c r="D90" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="25.5" customHeight="1">
@@ -1642,7 +1652,7 @@
         <v>7</v>
       </c>
       <c r="E95" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="25.5" customHeight="1">
@@ -1687,7 +1697,7 @@
         <v>18</v>
       </c>
       <c r="E98" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="25.5" customHeight="1">
@@ -1728,7 +1738,7 @@
         <v>10</v>
       </c>
       <c r="E102" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="25.5" customHeight="1">
@@ -1773,7 +1783,7 @@
         <v>7</v>
       </c>
       <c r="E105" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="25.5" customHeight="1">
@@ -1814,7 +1824,7 @@
         <v>19</v>
       </c>
       <c r="E109" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="25.5" customHeight="1">
@@ -1839,7 +1849,7 @@
         <v>11</v>
       </c>
       <c r="C111" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D111" t="s">
         <v>15</v>
@@ -1878,7 +1888,7 @@
         <v>46116</v>
       </c>
       <c r="E114" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="25.5" customHeight="1">
@@ -1886,7 +1896,7 @@
         <v>46117</v>
       </c>
       <c r="E115" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="25.5" customHeight="1">
@@ -1897,7 +1907,7 @@
         <v>5</v>
       </c>
       <c r="E116" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="25.5" customHeight="1">
@@ -1925,7 +1935,7 @@
         <v>6</v>
       </c>
       <c r="D118" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="25.5" customHeight="1">
@@ -1988,7 +1998,7 @@
         <v>8</v>
       </c>
       <c r="C124" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D124" t="s">
         <v>15</v>
@@ -2190,7 +2200,7 @@
         <v>17</v>
       </c>
       <c r="E141" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="25.5" customHeight="1">
@@ -2198,7 +2208,7 @@
         <v>46144</v>
       </c>
       <c r="E142" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="25.5" customHeight="1">
@@ -2206,7 +2216,7 @@
         <v>46145</v>
       </c>
       <c r="E143" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="25.5" customHeight="1">
@@ -2217,7 +2227,7 @@
         <v>5</v>
       </c>
       <c r="E144" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="25.5" customHeight="1">
@@ -2228,7 +2238,7 @@
         <v>8</v>
       </c>
       <c r="E145" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="25.5" customHeight="1">
@@ -2267,7 +2277,7 @@
         <v>17</v>
       </c>
       <c r="C148" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D148" t="s">
         <v>16</v>
@@ -2371,7 +2381,7 @@
         <v>5</v>
       </c>
       <c r="C158" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D158" t="s">
         <v>19</v>
@@ -2559,7 +2569,7 @@
         <v>11</v>
       </c>
       <c r="C174" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -2625,7 +2635,7 @@
         <v>8</v>
       </c>
       <c r="C180" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D180" t="s">
         <v>12</v>
@@ -2694,7 +2704,7 @@
         <v>12</v>
       </c>
       <c r="D186" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="25.5" customHeight="1">
@@ -2747,7 +2757,7 @@
         <v>17</v>
       </c>
       <c r="E190" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="25.5" customHeight="1">
@@ -2755,7 +2765,7 @@
         <v>46193</v>
       </c>
       <c r="E191" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="25.5" customHeight="1">
@@ -2763,7 +2773,7 @@
         <v>46194</v>
       </c>
       <c r="E192" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="25.5" customHeight="1">
@@ -2830,7 +2840,7 @@
         <v>17</v>
       </c>
       <c r="C197" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D197" t="s">
         <v>12</v>
@@ -2937,7 +2947,7 @@
         <v>16</v>
       </c>
       <c r="D207" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="25.5" customHeight="1">
@@ -3136,7 +3146,7 @@
         <v>14</v>
       </c>
       <c r="C224" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D224" t="s">
         <v>15</v>
@@ -3156,7 +3166,7 @@
         <v>10</v>
       </c>
       <c r="E225" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="226" spans="1:5" ht="25.5" customHeight="1">
@@ -3164,7 +3174,7 @@
         <v>46228</v>
       </c>
       <c r="E226" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="227" spans="1:5" ht="25.5" customHeight="1">
@@ -3172,7 +3182,7 @@
         <v>46229</v>
       </c>
       <c r="E227" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="228" spans="1:5" ht="25.5" customHeight="1">
@@ -3186,10 +3196,10 @@
         <v>19</v>
       </c>
       <c r="D228" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E228" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="229" spans="1:5" ht="25.5" customHeight="1">
@@ -3206,7 +3216,7 @@
         <v>10</v>
       </c>
       <c r="E229" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:5" ht="25.5" customHeight="1">
@@ -3223,7 +3233,7 @@
         <v>6</v>
       </c>
       <c r="E230" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="231" spans="1:5" ht="25.5" customHeight="1">
@@ -3240,7 +3250,7 @@
         <v>19</v>
       </c>
       <c r="E231" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="232" spans="1:5" ht="25.5" customHeight="1">
@@ -3257,7 +3267,7 @@
         <v>10</v>
       </c>
       <c r="E232" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="233" spans="1:5" ht="25.5" customHeight="1">
@@ -3295,7 +3305,7 @@
         <v>15</v>
       </c>
       <c r="D236" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="237" spans="1:5" ht="25.5" customHeight="1">
@@ -3361,7 +3371,7 @@
         <v>9</v>
       </c>
       <c r="D242" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="243" spans="1:5" ht="25.5" customHeight="1">
@@ -3420,7 +3430,7 @@
         <v>6</v>
       </c>
       <c r="E246" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="247" spans="1:5" ht="25.5" customHeight="1">
@@ -3444,7 +3454,7 @@
         <v>15</v>
       </c>
       <c r="D249" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="250" spans="1:5" ht="25.5" customHeight="1">
@@ -3472,7 +3482,7 @@
         <v>16</v>
       </c>
       <c r="D251" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="252" spans="1:5" ht="25.5" customHeight="1">
@@ -3486,7 +3496,7 @@
         <v>6</v>
       </c>
       <c r="D252" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="253" spans="1:5" ht="25.5" customHeight="1">
@@ -3497,7 +3507,7 @@
         <v>17</v>
       </c>
       <c r="C253" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D253" t="s">
         <v>19</v>
@@ -3524,7 +3534,7 @@
         <v>15</v>
       </c>
       <c r="D256" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="25.5" customHeight="1">
@@ -3535,7 +3545,7 @@
         <v>8</v>
       </c>
       <c r="C257" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D257" t="s">
         <v>16</v>
@@ -3549,7 +3559,7 @@
         <v>11</v>
       </c>
       <c r="C258" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D258" t="s">
         <v>6</v>
@@ -3577,10 +3587,10 @@
         <v>17</v>
       </c>
       <c r="C260" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D260" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="25.5" customHeight="1">
@@ -3601,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="C263" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D263" t="s">
         <v>16</v>
@@ -3657,7 +3667,7 @@
         <v>17</v>
       </c>
       <c r="C267" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -3681,10 +3691,10 @@
         <v>5</v>
       </c>
       <c r="C270" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D270" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="25.5" customHeight="1">
@@ -3740,7 +3750,7 @@
         <v>18</v>
       </c>
       <c r="D274" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="25.5" customHeight="1">
@@ -3761,7 +3771,7 @@
         <v>5</v>
       </c>
       <c r="C277" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D277" t="s">
         <v>15</v>

--- a/cmnrag-website/paiban-data/采访中心综合表格_2026值班.xlsx
+++ b/cmnrag-website/paiban-data/采访中心综合表格_2026值班.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C387F30-9DA7-4CB6-B121-987D2DB92DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{5C387F30-9DA7-4CB6-B121-987D2DB92DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD11DD00-4807-41C7-9C2B-AFF524A42B07}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,9 +99,6 @@
     <t>日</t>
   </si>
   <si>
-    <t>上班，做5日见报报纸</t>
-  </si>
-  <si>
     <t>6-9 钊哥一版审稿，亮哥二版审稿</t>
   </si>
   <si>
@@ -175,9 +172,6 @@
   </si>
   <si>
     <t>不要排赵宁</t>
-  </si>
-  <si>
-    <t>文科,郭笑羽</t>
   </si>
   <si>
     <t>郭笑羽</t>
@@ -193,6 +187,14 @@
   </si>
   <si>
     <t>吴彤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>文科</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上班，做5日见报报纸</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -811,7 +813,7 @@
         <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="25.5" customHeight="1">
@@ -842,7 +844,7 @@
         <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="25.5" customHeight="1">
@@ -991,7 +993,7 @@
         <v>19</v>
       </c>
       <c r="E39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="25.5" customHeight="1">
@@ -1036,7 +1038,7 @@
         <v>7</v>
       </c>
       <c r="E42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="25.5" customHeight="1">
@@ -1185,7 +1187,7 @@
         <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="25.5" customHeight="1">
@@ -1199,10 +1201,10 @@
         <v>12</v>
       </c>
       <c r="D56" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E56" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="25.5" customHeight="1">
@@ -1229,7 +1231,7 @@
         <v>46061</v>
       </c>
       <c r="E59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="25.5" customHeight="1">
@@ -1246,7 +1248,7 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="25.5" customHeight="1">
@@ -1302,10 +1304,10 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E64" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="25.5" customHeight="1">
@@ -1313,7 +1315,7 @@
         <v>46067</v>
       </c>
       <c r="E65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="25.5" customHeight="1">
@@ -1321,7 +1323,7 @@
         <v>46068</v>
       </c>
       <c r="E66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="25.5" customHeight="1">
@@ -1332,7 +1334,7 @@
         <v>5</v>
       </c>
       <c r="E67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="25.5" customHeight="1">
@@ -1343,7 +1345,7 @@
         <v>8</v>
       </c>
       <c r="E68" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="25.5" customHeight="1">
@@ -1354,7 +1356,7 @@
         <v>11</v>
       </c>
       <c r="E69" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="25.5" customHeight="1">
@@ -1365,7 +1367,7 @@
         <v>14</v>
       </c>
       <c r="E70" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="25.5" customHeight="1">
@@ -1376,7 +1378,7 @@
         <v>17</v>
       </c>
       <c r="E71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="25.5" customHeight="1">
@@ -1384,7 +1386,7 @@
         <v>46074</v>
       </c>
       <c r="E72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="25.5" customHeight="1">
@@ -1392,7 +1394,7 @@
         <v>46075</v>
       </c>
       <c r="E73" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="25.5" customHeight="1">
@@ -1403,7 +1405,7 @@
         <v>5</v>
       </c>
       <c r="E74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="25.5" customHeight="1">
@@ -1462,7 +1464,7 @@
         <v>18</v>
       </c>
       <c r="E78" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="25.5" customHeight="1">
@@ -1470,7 +1472,7 @@
         <v>46081</v>
       </c>
       <c r="E79" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="25.5" customHeight="1">
@@ -1486,7 +1488,7 @@
         <v>5</v>
       </c>
       <c r="C81" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D81" t="s">
         <v>15</v>
@@ -1500,7 +1502,7 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -1580,7 +1582,7 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -1597,7 +1599,7 @@
         <v>19</v>
       </c>
       <c r="D90" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="25.5" customHeight="1">
@@ -1652,7 +1654,7 @@
         <v>7</v>
       </c>
       <c r="E95" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="25.5" customHeight="1">
@@ -1697,7 +1699,7 @@
         <v>18</v>
       </c>
       <c r="E98" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="25.5" customHeight="1">
@@ -1738,7 +1740,7 @@
         <v>10</v>
       </c>
       <c r="E102" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="25.5" customHeight="1">
@@ -1783,7 +1785,7 @@
         <v>7</v>
       </c>
       <c r="E105" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="25.5" customHeight="1">
@@ -1824,7 +1826,7 @@
         <v>19</v>
       </c>
       <c r="E109" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="25.5" customHeight="1">
@@ -1849,7 +1851,7 @@
         <v>11</v>
       </c>
       <c r="C111" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D111" t="s">
         <v>15</v>
@@ -1888,7 +1890,7 @@
         <v>46116</v>
       </c>
       <c r="E114" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="25.5" customHeight="1">
@@ -1896,7 +1898,7 @@
         <v>46117</v>
       </c>
       <c r="E115" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="25.5" customHeight="1">
@@ -1907,7 +1909,7 @@
         <v>5</v>
       </c>
       <c r="E116" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="25.5" customHeight="1">
@@ -1935,7 +1937,7 @@
         <v>6</v>
       </c>
       <c r="D118" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="25.5" customHeight="1">
@@ -1998,7 +2000,7 @@
         <v>8</v>
       </c>
       <c r="C124" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D124" t="s">
         <v>15</v>
@@ -2200,7 +2202,7 @@
         <v>17</v>
       </c>
       <c r="E141" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="25.5" customHeight="1">
@@ -2208,7 +2210,7 @@
         <v>46144</v>
       </c>
       <c r="E142" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="25.5" customHeight="1">
@@ -2216,7 +2218,7 @@
         <v>46145</v>
       </c>
       <c r="E143" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="25.5" customHeight="1">
@@ -2227,7 +2229,7 @@
         <v>5</v>
       </c>
       <c r="E144" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="25.5" customHeight="1">
@@ -2238,7 +2240,7 @@
         <v>8</v>
       </c>
       <c r="E145" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="25.5" customHeight="1">
@@ -2277,7 +2279,7 @@
         <v>17</v>
       </c>
       <c r="C148" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D148" t="s">
         <v>16</v>
@@ -2381,7 +2383,7 @@
         <v>5</v>
       </c>
       <c r="C158" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D158" t="s">
         <v>19</v>
@@ -2569,7 +2571,7 @@
         <v>11</v>
       </c>
       <c r="C174" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -2635,7 +2637,7 @@
         <v>8</v>
       </c>
       <c r="C180" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D180" t="s">
         <v>12</v>
@@ -2704,7 +2706,7 @@
         <v>12</v>
       </c>
       <c r="D186" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="25.5" customHeight="1">
@@ -2757,7 +2759,7 @@
         <v>17</v>
       </c>
       <c r="E190" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="25.5" customHeight="1">
@@ -2765,7 +2767,7 @@
         <v>46193</v>
       </c>
       <c r="E191" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="25.5" customHeight="1">
@@ -2773,7 +2775,7 @@
         <v>46194</v>
       </c>
       <c r="E192" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="25.5" customHeight="1">
@@ -2840,7 +2842,7 @@
         <v>17</v>
       </c>
       <c r="C197" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D197" t="s">
         <v>12</v>
@@ -2947,7 +2949,7 @@
         <v>16</v>
       </c>
       <c r="D207" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="25.5" customHeight="1">
@@ -3146,7 +3148,7 @@
         <v>14</v>
       </c>
       <c r="C224" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D224" t="s">
         <v>15</v>
@@ -3166,7 +3168,7 @@
         <v>10</v>
       </c>
       <c r="E225" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="226" spans="1:5" ht="25.5" customHeight="1">
@@ -3174,7 +3176,7 @@
         <v>46228</v>
       </c>
       <c r="E226" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="227" spans="1:5" ht="25.5" customHeight="1">
@@ -3182,7 +3184,7 @@
         <v>46229</v>
       </c>
       <c r="E227" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="228" spans="1:5" ht="25.5" customHeight="1">
@@ -3196,10 +3198,10 @@
         <v>19</v>
       </c>
       <c r="D228" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E228" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="229" spans="1:5" ht="25.5" customHeight="1">
@@ -3216,7 +3218,7 @@
         <v>10</v>
       </c>
       <c r="E229" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="230" spans="1:5" ht="25.5" customHeight="1">
@@ -3233,7 +3235,7 @@
         <v>6</v>
       </c>
       <c r="E230" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="231" spans="1:5" ht="25.5" customHeight="1">
@@ -3250,7 +3252,7 @@
         <v>19</v>
       </c>
       <c r="E231" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="232" spans="1:5" ht="25.5" customHeight="1">
@@ -3267,7 +3269,7 @@
         <v>10</v>
       </c>
       <c r="E232" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="233" spans="1:5" ht="25.5" customHeight="1">
@@ -3305,7 +3307,7 @@
         <v>15</v>
       </c>
       <c r="D236" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="237" spans="1:5" ht="25.5" customHeight="1">
@@ -3371,7 +3373,7 @@
         <v>9</v>
       </c>
       <c r="D242" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="243" spans="1:5" ht="25.5" customHeight="1">
@@ -3430,7 +3432,7 @@
         <v>6</v>
       </c>
       <c r="E246" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="247" spans="1:5" ht="25.5" customHeight="1">
@@ -3454,7 +3456,7 @@
         <v>15</v>
       </c>
       <c r="D249" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="250" spans="1:5" ht="25.5" customHeight="1">
@@ -3587,7 +3589,7 @@
         <v>17</v>
       </c>
       <c r="C260" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D260" t="s">
         <v>18</v>
@@ -3611,7 +3613,7 @@
         <v>5</v>
       </c>
       <c r="C263" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D263" t="s">
         <v>16</v>
@@ -3694,7 +3696,7 @@
         <v>12</v>
       </c>
       <c r="D270" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="25.5" customHeight="1">
@@ -3750,7 +3752,7 @@
         <v>18</v>
       </c>
       <c r="D274" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="25.5" customHeight="1">
